--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.14680439154924</v>
+        <v>2.461355713626752</v>
       </c>
       <c r="D2" t="n">
-        <v>9.300443488572181</v>
+        <v>1.511322066892979</v>
       </c>
       <c r="E2" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F2" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.84320033502174</v>
+        <v>3.549520054441033</v>
       </c>
       <c r="D3" t="n">
-        <v>12.70805846232879</v>
+        <v>2.065059500128429</v>
       </c>
       <c r="E3" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F3" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.81922622083933</v>
+        <v>3.058124260886392</v>
       </c>
       <c r="D4" t="n">
-        <v>20.90933919125724</v>
+        <v>3.397767618579301</v>
       </c>
       <c r="E4" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F4" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.99021884525746</v>
+        <v>1.785910562354337</v>
       </c>
       <c r="D5" t="n">
-        <v>14.05586832113826</v>
+        <v>2.284078602184967</v>
       </c>
       <c r="E5" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F5" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.30320069188447</v>
+        <v>2.161770112431227</v>
       </c>
       <c r="D6" t="n">
-        <v>17.02251899953049</v>
+        <v>2.766159337423705</v>
       </c>
       <c r="E6" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F6" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.07078120985053</v>
+        <v>2.124001946600711</v>
       </c>
       <c r="D7" t="n">
-        <v>13.07078120985053</v>
+        <v>2.124001946600711</v>
       </c>
       <c r="E7" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F7" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.68834289377203</v>
+        <v>2.549355720237955</v>
       </c>
       <c r="D8" t="n">
-        <v>14.93898359671024</v>
+        <v>2.427584834465415</v>
       </c>
       <c r="E8" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F8" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>2.612316165204301</v>
+        <v>0.4245013768456989</v>
       </c>
       <c r="D9" t="n">
-        <v>2.451934114689415</v>
+        <v>0.39843929363703</v>
       </c>
       <c r="E9" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F9" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.406234160295753</v>
+        <v>1.36601305104806</v>
       </c>
       <c r="D10" t="n">
-        <v>6.933338651860251</v>
+        <v>1.126667530927291</v>
       </c>
       <c r="E10" t="n">
-        <v>5.334609801403946</v>
+        <v>0.8668740927281415</v>
       </c>
       <c r="F10" t="n">
-        <v>5.185026851390276</v>
+        <v>0.8425668633509199</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
